--- a/data/trans_camb/P16A03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A03-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,03</t>
+          <t>-2,48; -0,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; -0,05</t>
+          <t>-2,45; -0,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,48</t>
+          <t>-0,72; 2,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,1</t>
+          <t>-3,13; 1,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,74</t>
+          <t>-3,43; 1,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,29</t>
+          <t>-3,59; 0,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,44</t>
+          <t>-2,35; 0,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,28</t>
+          <t>-2,39; 0,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,93</t>
+          <t>-1,73; 0,91</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-84,45; 14,26</t>
+          <t>-85,68; 11,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-91,23; 9,72</t>
+          <t>-85,99; 25,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 216,27</t>
+          <t>-30,64; 195,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,21; 44,3</t>
+          <t>-42,06; 45,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,01; 39,58</t>
+          <t>-45,94; 38,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 6,19</t>
+          <t>-48,4; 10,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,75; 15,08</t>
+          <t>-49,19; 21,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,54; 9,02</t>
+          <t>-51,58; 12,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 30,06</t>
+          <t>-35,29; 29,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,17</t>
+          <t>-2,49; -0,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; -0,12</t>
+          <t>-2,63; -0,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,09</t>
+          <t>-2,56; 0,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,25</t>
+          <t>-1,12; 3,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; -0,51</t>
+          <t>-4,41; -0,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,82</t>
+          <t>-2,78; 0,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,11</t>
+          <t>-1,36; 1,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,73</t>
+          <t>-3,0; -0,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; -0,06</t>
+          <t>-2,66; -0,19</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-80,56; 0,06</t>
+          <t>-77,51; 8,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,72; 4,55</t>
+          <t>-77,43; 7,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-79,12; 6,99</t>
+          <t>-77,76; 11,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 71,84</t>
+          <t>-17,36; 71,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,9; -10,33</t>
+          <t>-66,76; -9,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,65; 19,6</t>
+          <t>-41,66; 18,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 34,32</t>
+          <t>-29,28; 34,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,64; -21,43</t>
+          <t>-63,36; -19,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,66; -3,91</t>
+          <t>-55,53; -5,74</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,58</t>
+          <t>-1,71; 1,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,23</t>
+          <t>-1,71; 1,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,15</t>
+          <t>-0,99; 2,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,9</t>
+          <t>-1,8; 3,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,56</t>
+          <t>-3,57; 0,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 0,29</t>
+          <t>-4,81; 0,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,86</t>
+          <t>-1,15; 1,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,36</t>
+          <t>-2,19; 0,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,71</t>
+          <t>-2,24; 0,68</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,8; 202,95</t>
+          <t>-68,69; 187,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-66,99; 131,55</t>
+          <t>-65,3; 132,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,53; 244,66</t>
+          <t>-42,89; 236,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 69,28</t>
+          <t>-26,58; 78,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-57,99; 14,31</t>
+          <t>-54,88; 20,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,41; 5,53</t>
+          <t>-71,05; 5,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,01; 66,29</t>
+          <t>-26,61; 71,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,01; 14,35</t>
+          <t>-49,85; 24,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 26,43</t>
+          <t>-51,82; 22,72</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,2</t>
+          <t>-2,2; 0,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,25</t>
+          <t>-2,41; 0,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,9</t>
+          <t>-1,82; 0,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,12</t>
+          <t>-0,77; 3,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,06</t>
+          <t>-1,81; 1,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 4,1</t>
+          <t>0,17; 4,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,38</t>
+          <t>-1,03; 1,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,66</t>
+          <t>-1,58; 0,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,27</t>
+          <t>-0,18; 2,22</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,72; 16,47</t>
+          <t>-67,92; 17,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-68,85; 18,44</t>
+          <t>-69,65; 10,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,84; 52,36</t>
+          <t>-55,71; 41,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 83,41</t>
+          <t>-15,19; 85,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 57,17</t>
+          <t>-32,67; 50,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 105,28</t>
+          <t>2,8; 108,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,88; 43,26</t>
+          <t>-24,26; 44,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,21; 21,15</t>
+          <t>-37,56; 21,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 71,3</t>
+          <t>-5,26; 69,16</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; -0,23</t>
+          <t>-1,58; -0,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,64; -0,32</t>
+          <t>-1,61; -0,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,5</t>
+          <t>-1,1; 0,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,81</t>
+          <t>-0,47; 1,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,23; -0,04</t>
+          <t>-2,36; -0,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,65</t>
+          <t>-1,54; 0,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,58</t>
+          <t>-0,72; 0,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; -0,46</t>
+          <t>-1,65; -0,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,37</t>
+          <t>-0,96; 0,38</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-59,11; -11,67</t>
+          <t>-61,17; -12,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-61,24; -16,92</t>
+          <t>-60,5; -15,87</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,26; 27,09</t>
+          <t>-40,54; 22,73</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 37,79</t>
+          <t>-8,14; 37,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 0,45</t>
+          <t>-40,08; -3,02</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 13,09</t>
+          <t>-26,33; 13,14</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 17,27</t>
+          <t>-17,38; 19,7</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-40,7; -12,68</t>
+          <t>-39,86; -12,22</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 10,85</t>
+          <t>-23,47; 11,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A03-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-1,6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,36</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; -0,02</t>
+          <t>-2,48; 0,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; -0,02</t>
+          <t>-2,52; 0,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,41</t>
+          <t>-0,66; 2,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 1,99</t>
+          <t>-3,01; 1,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,66</t>
+          <t>-3,32; 1,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,45</t>
+          <t>-3,75; 0,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 0,6</t>
+          <t>-2,19; 0,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,39</t>
+          <t>-2,34; 0,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,91</t>
+          <t>-1,74; 0,94</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-25,48%</t>
+          <t>-26,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-8,01%</t>
+          <t>-9,25%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-85,68; 11,82</t>
+          <t>-86,15; 28,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,99; 25,32</t>
+          <t>-89,09; 26,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 195,7</t>
+          <t>-26,76; 215,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,06; 45,71</t>
+          <t>-43,1; 41,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,94; 38,82</t>
+          <t>-45,66; 37,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,4; 10,54</t>
+          <t>-49,34; 9,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,19; 21,87</t>
+          <t>-46,81; 17,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,58; 12,42</t>
+          <t>-51,0; 14,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,29; 29,89</t>
+          <t>-35,71; 30,85</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,11</t>
+          <t>-0,84</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,22 +865,22 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>-1,0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-0,12</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-1,83</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>-0,91</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-1,83</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; -0,02</t>
+          <t>-2,83; -0,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; -0,11</t>
+          <t>-2,74; -0,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,25</t>
+          <t>-2,26; 0,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,2</t>
+          <t>-1,08; 3,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,41; -0,48</t>
+          <t>-4,18; -0,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,83</t>
+          <t>-3,01; 0,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,12</t>
+          <t>-1,4; 1,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; -0,68</t>
+          <t>-3,03; -0,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; -0,19</t>
+          <t>-2,16; 0,15</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-45,59%</t>
+          <t>-34,36%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-16,55%</t>
+          <t>-18,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-30,04%</t>
+          <t>-22,83%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,51; 8,19</t>
+          <t>-81,6; 2,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,43; 7,43</t>
+          <t>-81,93; 0,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,76; 11,04</t>
+          <t>-66,21; 23,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 71,05</t>
+          <t>-17,26; 67,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,76; -9,59</t>
+          <t>-64,61; -13,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,66; 18,39</t>
+          <t>-42,62; 14,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 34,78</t>
+          <t>-30,3; 37,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,36; -19,3</t>
+          <t>-64,0; -22,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,53; -5,74</t>
+          <t>-43,33; 5,59</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,93</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>0,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,65</t>
+          <t>-1,64; 1,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,19</t>
+          <t>-1,75; 1,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,02</t>
+          <t>-0,63; 2,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,28</t>
+          <t>-1,83; 3,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 0,72</t>
+          <t>-3,81; 0,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 0,29</t>
+          <t>-2,92; 1,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,94</t>
+          <t>-1,26; 1,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 0,68</t>
+          <t>-2,19; 0,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,68</t>
+          <t>-1,22; 1,68</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-35,99%</t>
+          <t>-10,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-17,25%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,69; 187,09</t>
+          <t>-68,55; 208,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-65,3; 132,09</t>
+          <t>-66,43; 136,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-42,89; 236,63</t>
+          <t>-33,09; 285,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,58; 78,95</t>
+          <t>-27,63; 77,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,88; 20,14</t>
+          <t>-55,55; 15,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,05; 5,05</t>
+          <t>-41,71; 40,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 71,05</t>
+          <t>-29,51; 65,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,85; 24,94</t>
+          <t>-50,51; 14,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-51,82; 22,72</t>
+          <t>-27,35; 62,06</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>2,56</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,21</t>
+          <t>-2,24; 0,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,16</t>
+          <t>-2,4; 0,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,82</t>
+          <t>-1,98; 0,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,3</t>
+          <t>-0,9; 3,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,88</t>
+          <t>-1,78; 1,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 4,19</t>
+          <t>0,69; 4,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,39</t>
+          <t>-1,06; 1,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,67</t>
+          <t>-1,7; 0,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,22</t>
+          <t>-0,12; 2,28</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-19,83%</t>
+          <t>-23,18%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,92; 17,73</t>
+          <t>-70,42; 9,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,65; 10,43</t>
+          <t>-70,88; 13,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,71; 41,15</t>
+          <t>-57,31; 29,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 85,76</t>
+          <t>-17,52; 78,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 50,42</t>
+          <t>-32,99; 53,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,8; 108,51</t>
+          <t>9,06; 121,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,26; 44,58</t>
+          <t>-24,75; 41,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 21,88</t>
+          <t>-38,68; 20,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 69,16</t>
+          <t>-3,49; 70,76</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>0,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,58; -0,25</t>
+          <t>-1,58; -0,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; -0,3</t>
+          <t>-1,68; -0,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,41</t>
+          <t>-0,8; 0,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,74</t>
+          <t>-0,49; 1,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,36; -0,14</t>
+          <t>-2,24; -0,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,61</t>
+          <t>-0,98; 0,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,67</t>
+          <t>-0,76; 0,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; -0,43</t>
+          <t>-1,66; -0,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,38</t>
+          <t>-0,64; 0,58</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-10,97%</t>
+          <t>-2,48%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-6,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-7,56%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-61,17; -12,84</t>
+          <t>-61,02; -10,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-60,5; -15,87</t>
+          <t>-63,34; -16,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 22,73</t>
+          <t>-30,88; 33,52</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 37,26</t>
+          <t>-8,75; 37,27</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,08; -3,02</t>
+          <t>-37,43; -2,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-26,33; 13,14</t>
+          <t>-16,28; 20,5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 19,7</t>
+          <t>-18,28; 16,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-39,86; -12,22</t>
+          <t>-39,26; -13,36</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 11,58</t>
+          <t>-15,26; 16,7</t>
         </is>
       </c>
     </row>
